--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.92095990447714</v>
+        <v>8.599655984477536</v>
       </c>
       <c r="D2" t="n">
-        <v>76.98998830036211</v>
+        <v>12.51087309880884</v>
       </c>
       <c r="E2" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F2" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.90849137207189</v>
+        <v>4.697629847961683</v>
       </c>
       <c r="D3" t="n">
-        <v>38.66017193150994</v>
+        <v>6.282277938870365</v>
       </c>
       <c r="E3" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F3" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.7607978442466</v>
+        <v>7.598629649690072</v>
       </c>
       <c r="D4" t="n">
-        <v>36.71827086842057</v>
+        <v>5.966719016118343</v>
       </c>
       <c r="E4" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F4" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.44335370319703</v>
+        <v>8.522044976769518</v>
       </c>
       <c r="D5" t="n">
-        <v>39.81190177185852</v>
+        <v>6.469434037927011</v>
       </c>
       <c r="E5" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F5" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.14614560571171</v>
+        <v>4.411248660928154</v>
       </c>
       <c r="D6" t="n">
-        <v>48.13444797809804</v>
+        <v>7.821847796440933</v>
       </c>
       <c r="E6" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F6" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.80074329015907</v>
+        <v>1.105120784650849</v>
       </c>
       <c r="D7" t="n">
-        <v>23.05024096120113</v>
+        <v>3.745664156195184</v>
       </c>
       <c r="E7" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F7" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.770102597694317</v>
+        <v>1.425141672125326</v>
       </c>
       <c r="D8" t="n">
-        <v>14.43086968966181</v>
+        <v>2.345016324570044</v>
       </c>
       <c r="E8" t="n">
-        <v>18.05245349733642</v>
+        <v>2.933523693317169</v>
       </c>
       <c r="F8" t="n">
-        <v>18.46776917261712</v>
+        <v>3.001012490550282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
